--- a/experiment/ELAN_bestx8/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/ELAN_bestx8/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.22</v>
+        <v>24.62</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5536</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.41</v>
+        <v>26.58</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5568</v>
+        <v>0.6558</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.24</v>
+        <v>23.23</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5081</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.21</v>
+        <v>29.83</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7226</v>
+        <v>0.8673</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.74</v>
+        <v>32.09</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7768</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.01</v>
+        <v>24.57</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5971</v>
+        <v>0.7649</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.04</v>
+        <v>26.12</v>
       </c>
       <c r="C8" t="n">
-        <v>0.652</v>
+        <v>0.8622</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.06</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6236</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.92</v>
+        <v>24.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5684</v>
+        <v>0.7691</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20.97</v>
+        <v>24.27</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5885</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.53</v>
+        <v>22.47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5917</v>
+        <v>0.8093</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.45</v>
+        <v>22.37</v>
       </c>
       <c r="C13" t="n">
-        <v>0.451</v>
+        <v>0.6492</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.97</v>
+        <v>25.58</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.8722</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.36</v>
+        <v>25.66</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6279</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.52</v>
+        <v>23.69</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5679</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.18</v>
+        <v>21.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0.544</v>
+        <v>0.7063</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.04</v>
+        <v>23.99</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6075</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.05</v>
+        <v>28.58</v>
       </c>
       <c r="C19" t="n">
-        <v>0.819</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25.65</v>
+        <v>27.51</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7346</v>
+        <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.62</v>
+        <v>26.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.793</v>
+        <v>0.9092</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.65</v>
+        <v>25.85</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6214</v>
+        <v>0.7774</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20.52</v>
+        <v>25.84</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5759</v>
+        <v>0.7933</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.07</v>
+        <v>24.63</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6166</v>
+        <v>0.7801</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24.02</v>
+        <v>29.38</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7265</v>
+        <v>0.9198</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.58</v>
+        <v>22.45</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6703</v>
+        <v>0.8562</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>24.44</v>
       </c>
       <c r="C27" t="n">
-        <v>0.637</v>
+        <v>0.8249</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23.01</v>
+        <v>29.69</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7232</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23.7</v>
+        <v>26.72</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6783</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.64</v>
+        <v>26.13</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6919</v>
+        <v>0.8764999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23.35</v>
+        <v>25.87</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6605</v>
+        <v>0.8372000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.23</v>
+        <v>19.66</v>
       </c>
       <c r="C32" t="n">
-        <v>0.492</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.7</v>
+        <v>20.8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5366</v>
+        <v>0.7254</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24.33</v>
+        <v>27.42</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6128</v>
+        <v>0.7568</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.76</v>
+        <v>24.46</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4641</v>
+        <v>0.6038</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.89</v>
+        <v>21.34</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5059</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.49</v>
+        <v>25.22</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5939</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.84</v>
+        <v>23.4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5633</v>
+        <v>0.7365</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21.69</v>
+        <v>27.42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7002</v>
+        <v>0.8892</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25.19</v>
+        <v>27.36</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7028</v>
+        <v>0.8655</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.89</v>
+        <v>22.39</v>
       </c>
       <c r="C41" t="n">
-        <v>0.482</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.84</v>
+        <v>24.57</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5047</v>
+        <v>0.6614</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.2</v>
+        <v>27.19</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7853</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.18</v>
+        <v>17.66</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3437</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23.62</v>
+        <v>27.59</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7569</v>
+        <v>0.8958</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.05</v>
+        <v>21.63</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7118</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.65</v>
+        <v>22.42</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5609</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25.9</v>
+        <v>28.98</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6936</v>
+        <v>0.8642</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.14</v>
+        <v>22.49</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20.73</v>
+        <v>22.85</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5455</v>
+        <v>0.7338</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21.65</v>
+        <v>23.33</v>
       </c>
       <c r="C51" t="n">
-        <v>0.485</v>
+        <v>0.6168</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21.37</v>
+        <v>24.28</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6783</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23.14</v>
+        <v>27.57</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6683</v>
+        <v>0.8519</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30.15</v>
+        <v>32.49</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7419</v>
+        <v>0.8423</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24.39</v>
+        <v>28.53</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7149</v>
+        <v>0.8682</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>18.75</v>
+        <v>19.64</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3505</v>
+        <v>0.4553</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>22.81</v>
+        <v>26.89</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7431</v>
+        <v>0.9051</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>19.83</v>
+        <v>22.53</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6156</v>
+        <v>0.8297</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>21.73</v>
+        <v>24.69</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6068</v>
+        <v>0.8107</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>20.17</v>
+        <v>21.2</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4662</v>
+        <v>0.5758</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.25</v>
+        <v>27</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7579</v>
+        <v>0.9063</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>20.7</v>
+        <v>25.31</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6006</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20.93</v>
+        <v>24.55</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.8279</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.29</v>
+        <v>27.47</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6621</v>
+        <v>0.8856000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.88</v>
+        <v>28.82</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6901</v>
+        <v>0.8417</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>19.06</v>
+        <v>20.85</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6479</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>21.86</v>
+        <v>24.98</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6546</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>21.54</v>
+        <v>26.57</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8234</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.83</v>
+        <v>25.29</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6168</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>20.3</v>
+        <v>22.76</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5631</v>
+        <v>0.7577</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>20.79</v>
+        <v>24.68</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6098</v>
+        <v>0.8146</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23.74</v>
+        <v>25.05</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4935</v>
+        <v>0.5961</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23.8</v>
+        <v>28.06</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7259</v>
+        <v>0.8747</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>23.32</v>
+        <v>27.08</v>
       </c>
       <c r="C74" t="n">
-        <v>0.679</v>
+        <v>0.8542</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>19.92</v>
+        <v>22</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5501</v>
+        <v>0.7017</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21.98</v>
+        <v>24.84</v>
       </c>
       <c r="C76" t="n">
-        <v>0.5814</v>
+        <v>0.7638</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20.85</v>
+        <v>23.8</v>
       </c>
       <c r="C77" t="n">
-        <v>0.6997</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>21.57</v>
+        <v>24.13</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5794</v>
+        <v>0.7104</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>19.21</v>
+        <v>22.75</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5236</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>22.86</v>
+        <v>25.77</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6757</v>
+        <v>0.8235</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>24.01</v>
+        <v>25.82</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6916</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21.42</v>
+        <v>24.39</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5179</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23.25</v>
+        <v>26.9</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5881</v>
+        <v>0.7747000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>19.74</v>
+        <v>23.46</v>
       </c>
       <c r="C84" t="n">
-        <v>0.637</v>
+        <v>0.8479</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>17.78</v>
+        <v>20.6</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6037</v>
+        <v>0.8052</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>22.97</v>
+        <v>25.91</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6106</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>21.6</v>
+        <v>24.2</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5876</v>
+        <v>0.7227</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>25</v>
+        <v>29.03</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7025</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>23</v>
+        <v>26.84</v>
       </c>
       <c r="C89" t="n">
-        <v>0.6917</v>
+        <v>0.8915999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>21.51</v>
+        <v>25.26</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6682</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>17.87</v>
+        <v>19.99</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4825</v>
+        <v>0.6633</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>20.65</v>
+        <v>23.09</v>
       </c>
       <c r="C92" t="n">
-        <v>0.5491</v>
+        <v>0.7197</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>17.48</v>
+        <v>21.35</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6766</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>15.94</v>
+        <v>17.58</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3172</v>
+        <v>0.4857</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>23.1</v>
+        <v>26.42</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7086</v>
+        <v>0.8636</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>18.38</v>
+        <v>20.93</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.6903</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>19.9</v>
+        <v>23.23</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5945</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.41</v>
+        <v>28.63</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6351</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18.77</v>
+        <v>22.86</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6428</v>
+        <v>0.8699</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>20.37</v>
+        <v>21.94</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3777</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>16.66</v>
+        <v>18.52</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4801</v>
+        <v>0.6782</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>21.43</v>
+        <v>23.09</v>
       </c>
       <c r="C102" t="n">
-        <v>0.624</v>
+        <v>0.7599</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>17.53</v>
+        <v>17.92</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2706</v>
+        <v>0.3284</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>23.8</v>
+        <v>28.07</v>
       </c>
       <c r="C104" t="n">
-        <v>0.7271</v>
+        <v>0.8973</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>21.2</v>
+        <v>23.33</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6313</v>
+        <v>0.7758</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>19.84</v>
+        <v>25</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6175</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>21.66</v>
+        <v>24.47</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5393</v>
+        <v>0.7296</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>26.21</v>
+        <v>29.29</v>
       </c>
       <c r="C108" t="n">
-        <v>0.7084</v>
+        <v>0.8532999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>23.89</v>
+        <v>26.76</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5766</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>22.16</v>
+        <v>24.24</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6311</v>
+        <v>0.7765</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>21.58</v>
+        <v>24.71</v>
       </c>
       <c r="C111" t="n">
-        <v>0.6082</v>
+        <v>0.777</v>
       </c>
     </row>
   </sheetData>
